--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -6449,7 +6449,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="N8" s="431">
-        <v>0.999164</v>
+        <v>0.999177</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18T09:01:38.255Z</t>
+          <t>2026-09-18T09:14:29.228Z</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
         <v>BNB / USDT</v>
       </c>
       <c r="N12">
-        <v>754.5107710045597</v>
+        <v>754.1006248142221</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:01:38.255Z</t>
+          <t>2026-09-18T09:14:29.228Z</t>
         </is>
       </c>
     </row>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Rcb50215a37fb4076"/>
-    <sheet name="控筹测算" sheetId="2" r:id="R6df3cdb0a3a8442f"/>
-    <sheet name="内外盘曲线" sheetId="3" r:id="Rc561d916392a4ad0"/>
-    <sheet name="洗筹明细" sheetId="4" r:id="Rc06c2cd2ebfe4d68"/>
-    <sheet name="参数与来源" sheetId="5" r:id="Rf606e03640024b06"/>
+    <sheet name="控筹模型" sheetId="1" r:id="Rffe7e1a924f44acc"/>
+    <sheet name="控筹测算" sheetId="2" r:id="Rd15db576cb5b4c33"/>
+    <sheet name="内外盘曲线" sheetId="3" r:id="R5319507f9c6c4c5e"/>
+    <sheet name="洗筹明细" sheetId="4" r:id="R0e2c89e81b7e455c"/>
+    <sheet name="参数与来源" sheetId="5" r:id="R65d0f1aaffda4dd3"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -475,7 +475,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="434">
+  <x:cellXfs count="436">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1638,6 +1638,8 @@
     <x:xf numFmtId="200" fontId="20" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="208" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1916,7 +1918,7 @@
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="C3" s="124" t="str">
-        <v>黄色格可编辑。预留按 10,000 USDT ÷ BNC4 价格向上取整；未填价格时建议总资金留空。Gas 单独以 BNB 计价。</v>
+        <v>黄色格可编辑。手动价格留空用指定池每日价；预留按 10,000 USDT ÷ 有效价格向上取整。Gas 单独以 BNB 计价。</v>
       </c>
       <c r="D3" s="124"/>
       <c r="E3" s="124"/>
@@ -2043,7 +2045,7 @@
         <v>资金预留 / BNC4</v>
       </c>
       <c r="H8" s="432">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),ROUNDUP('参数与来源'!$N$11/$L$14,0),"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),ROUNDUP('参数与来源'!$N$11/'参数与来源'!$N$19,0),"")</f>
       </c>
       <c r="I8" s="130" t="str">
         <v>额外内盘资金</v>
@@ -2244,7 +2246,7 @@
         <v>0.01</v>
       </c>
       <c r="K14" s="131" t="str">
-        <v>BNC4 / USDT 价格</v>
+        <v>手动价格 / USDT</v>
       </c>
       <c r="L14" s="220"/>
     </row>
@@ -2257,8 +2259,12 @@
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
+      <c r="K15" s="23" t="str">
+        <v>有效价格 / USDT</v>
+      </c>
+      <c r="L15" s="435">
+        <f>'参数与来源'!$N$19</f>
+      </c>
     </row>
     <row r="16">
       <c r="C16" s="23"/>
@@ -2338,13 +2344,13 @@
         <f>E19/D19</f>
       </c>
       <c r="H19" s="275">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G19))),"",G19*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G19))),"",G19*'参数与来源'!$N$19)</f>
       </c>
       <c r="I19" s="279">
         <f>G19*'参数与来源'!$D$8</f>
       </c>
       <c r="J19" s="279">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I19*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I19*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K19" s="279">
         <f>0</f>
@@ -2373,13 +2379,13 @@
         <f>E20/D20</f>
       </c>
       <c r="H20" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G20))),"",G20*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G20))),"",G20*'参数与来源'!$N$19)</f>
       </c>
       <c r="I20" s="298">
         <f>G20*'参数与来源'!$D$8</f>
       </c>
       <c r="J20" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I20*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I20*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K20" s="298">
         <f>E20-E19</f>
@@ -2408,13 +2414,13 @@
         <f>E21/D21</f>
       </c>
       <c r="H21" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G21))),"",G21*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G21))),"",G21*'参数与来源'!$N$19)</f>
       </c>
       <c r="I21" s="298">
         <f>G21*'参数与来源'!$D$8</f>
       </c>
       <c r="J21" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I21*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I21*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K21" s="298">
         <f>E21-E20</f>
@@ -2443,13 +2449,13 @@
         <f>E22/D22</f>
       </c>
       <c r="H22" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G22))),"",G22*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G22))),"",G22*'参数与来源'!$N$19)</f>
       </c>
       <c r="I22" s="298">
         <f>G22*'参数与来源'!$D$8</f>
       </c>
       <c r="J22" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I22*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I22*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K22" s="298">
         <f>E22-E21</f>
@@ -2478,13 +2484,13 @@
         <f>E23/D23</f>
       </c>
       <c r="H23" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G23))),"",G23*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G23))),"",G23*'参数与来源'!$N$19)</f>
       </c>
       <c r="I23" s="298">
         <f>G23*'参数与来源'!$D$8</f>
       </c>
       <c r="J23" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I23*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I23*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K23" s="298">
         <f>E23-E22</f>
@@ -2513,13 +2519,13 @@
         <f>E24/D24</f>
       </c>
       <c r="H24" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G24))),"",G24*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G24))),"",G24*'参数与来源'!$N$19)</f>
       </c>
       <c r="I24" s="298">
         <f>G24*'参数与来源'!$D$8</f>
       </c>
       <c r="J24" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I24*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I24*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K24" s="298">
         <f>E24-E23</f>
@@ -2548,13 +2554,13 @@
         <f>E25/D25</f>
       </c>
       <c r="H25" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G25))),"",G25*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G25))),"",G25*'参数与来源'!$N$19)</f>
       </c>
       <c r="I25" s="298">
         <f>G25*'参数与来源'!$D$8</f>
       </c>
       <c r="J25" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I25*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I25*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K25" s="298">
         <f>E25-E24</f>
@@ -2583,13 +2589,13 @@
         <f>E26/D26</f>
       </c>
       <c r="H26" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G26))),"",G26*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G26))),"",G26*'参数与来源'!$N$19)</f>
       </c>
       <c r="I26" s="298">
         <f>G26*'参数与来源'!$D$8</f>
       </c>
       <c r="J26" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I26*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I26*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K26" s="298">
         <f>E26-E25</f>
@@ -2618,13 +2624,13 @@
         <f>E27/D27</f>
       </c>
       <c r="H27" s="307">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G27))),"",G27*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G27))),"",G27*'参数与来源'!$N$19)</f>
       </c>
       <c r="I27" s="311">
         <f>G27*'参数与来源'!$D$8</f>
       </c>
       <c r="J27" s="311">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I27*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I27*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K27" s="311">
         <f>E27-E26</f>
@@ -2726,13 +2732,13 @@
         <f>IF(D32="","",E32/D32)</f>
       </c>
       <c r="H32" s="320">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G32))),"",G32*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G32))),"",G32*'参数与来源'!$N$19)</f>
       </c>
       <c r="I32" s="324">
         <f>IF(G32="","",G32*'参数与来源'!$D$8)</f>
       </c>
       <c r="J32" s="324">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I32=""),"",I32*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I32=""),"",I32*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K32" s="324">
         <f>IF(E32="","",(E32-$F$8)/(1-$F$11))</f>
@@ -2761,13 +2767,13 @@
         <f>IF(D33="","",E33/D33)</f>
       </c>
       <c r="H33" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G33))),"",G33*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G33))),"",G33*'参数与来源'!$N$19)</f>
       </c>
       <c r="I33" s="298">
         <f>IF(G33="","",G33*'参数与来源'!$D$8)</f>
       </c>
       <c r="J33" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I33=""),"",I33*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I33=""),"",I33*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K33" s="298">
         <f>IF(E33="","",(E33-$F$8)/(1-$F$11))</f>
@@ -2796,13 +2802,13 @@
         <f>IF(D34="","",E34/D34)</f>
       </c>
       <c r="H34" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G34))),"",G34*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G34))),"",G34*'参数与来源'!$N$19)</f>
       </c>
       <c r="I34" s="298">
         <f>IF(G34="","",G34*'参数与来源'!$D$8)</f>
       </c>
       <c r="J34" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I34=""),"",I34*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I34=""),"",I34*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K34" s="298">
         <f>IF(E34="","",(E34-$F$8)/(1-$F$11))</f>
@@ -2831,13 +2837,13 @@
         <f>IF(D35="","",E35/D35)</f>
       </c>
       <c r="H35" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G35))),"",G35*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G35))),"",G35*'参数与来源'!$N$19)</f>
       </c>
       <c r="I35" s="298">
         <f>IF(G35="","",G35*'参数与来源'!$D$8)</f>
       </c>
       <c r="J35" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I35=""),"",I35*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I35=""),"",I35*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K35" s="298">
         <f>IF(E35="","",(E35-$F$8)/(1-$F$11))</f>
@@ -2866,13 +2872,13 @@
         <f>IF(D36="","",E36/D36)</f>
       </c>
       <c r="H36" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G36))),"",G36*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G36))),"",G36*'参数与来源'!$N$19)</f>
       </c>
       <c r="I36" s="298">
         <f>IF(G36="","",G36*'参数与来源'!$D$8)</f>
       </c>
       <c r="J36" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I36=""),"",I36*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I36=""),"",I36*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K36" s="298">
         <f>IF(E36="","",(E36-$F$8)/(1-$F$11))</f>
@@ -2901,13 +2907,13 @@
         <f>IF(D37="","",E37/D37)</f>
       </c>
       <c r="H37" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G37))),"",G37*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G37))),"",G37*'参数与来源'!$N$19)</f>
       </c>
       <c r="I37" s="298">
         <f>IF(G37="","",G37*'参数与来源'!$D$8)</f>
       </c>
       <c r="J37" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I37=""),"",I37*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I37=""),"",I37*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K37" s="298">
         <f>IF(E37="","",(E37-$F$8)/(1-$F$11))</f>
@@ -2936,13 +2942,13 @@
         <f>IF(D38="","",E38/D38)</f>
       </c>
       <c r="H38" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G38))),"",G38*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G38))),"",G38*'参数与来源'!$N$19)</f>
       </c>
       <c r="I38" s="298">
         <f>IF(G38="","",G38*'参数与来源'!$D$8)</f>
       </c>
       <c r="J38" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I38=""),"",I38*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I38=""),"",I38*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K38" s="298">
         <f>IF(E38="","",(E38-$F$8)/(1-$F$11))</f>
@@ -2971,13 +2977,13 @@
         <f>IF(D39="","",E39/D39)</f>
       </c>
       <c r="H39" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G39))),"",G39*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G39))),"",G39*'参数与来源'!$N$19)</f>
       </c>
       <c r="I39" s="298">
         <f>IF(G39="","",G39*'参数与来源'!$D$8)</f>
       </c>
       <c r="J39" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I39=""),"",I39*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I39=""),"",I39*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K39" s="298">
         <f>IF(E39="","",(E39-$F$8)/(1-$F$11))</f>
@@ -3006,13 +3012,13 @@
         <f>IF(D40="","",E40/D40)</f>
       </c>
       <c r="H40" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G40))),"",G40*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G40))),"",G40*'参数与来源'!$N$19)</f>
       </c>
       <c r="I40" s="298">
         <f>IF(G40="","",G40*'参数与来源'!$D$8)</f>
       </c>
       <c r="J40" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I40=""),"",I40*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I40=""),"",I40*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K40" s="298">
         <f>IF(E40="","",(E40-$F$8)/(1-$F$11))</f>
@@ -3041,13 +3047,13 @@
         <f>IF(D41="","",E41/D41)</f>
       </c>
       <c r="H41" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G41))),"",G41*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G41))),"",G41*'参数与来源'!$N$19)</f>
       </c>
       <c r="I41" s="298">
         <f>IF(G41="","",G41*'参数与来源'!$D$8)</f>
       </c>
       <c r="J41" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I41=""),"",I41*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I41=""),"",I41*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K41" s="298">
         <f>IF(E41="","",(E41-$F$8)/(1-$F$11))</f>
@@ -3076,13 +3082,13 @@
         <f>IF(D42="","",E42/D42)</f>
       </c>
       <c r="H42" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G42))),"",G42*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G42))),"",G42*'参数与来源'!$N$19)</f>
       </c>
       <c r="I42" s="298">
         <f>IF(G42="","",G42*'参数与来源'!$D$8)</f>
       </c>
       <c r="J42" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I42=""),"",I42*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I42=""),"",I42*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K42" s="298">
         <f>IF(E42="","",(E42-$F$8)/(1-$F$11))</f>
@@ -3111,13 +3117,13 @@
         <f>IF(D43="","",E43/D43)</f>
       </c>
       <c r="H43" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G43))),"",G43*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G43))),"",G43*'参数与来源'!$N$19)</f>
       </c>
       <c r="I43" s="298">
         <f>IF(G43="","",G43*'参数与来源'!$D$8)</f>
       </c>
       <c r="J43" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I43=""),"",I43*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I43=""),"",I43*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K43" s="298">
         <f>IF(E43="","",(E43-$F$8)/(1-$F$11))</f>
@@ -3146,13 +3152,13 @@
         <f>IF(D44="","",E44/D44)</f>
       </c>
       <c r="H44" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G44))),"",G44*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G44))),"",G44*'参数与来源'!$N$19)</f>
       </c>
       <c r="I44" s="298">
         <f>IF(G44="","",G44*'参数与来源'!$D$8)</f>
       </c>
       <c r="J44" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I44=""),"",I44*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I44=""),"",I44*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K44" s="298">
         <f>IF(E44="","",(E44-$F$8)/(1-$F$11))</f>
@@ -3181,13 +3187,13 @@
         <f>IF(D45="","",E45/D45)</f>
       </c>
       <c r="H45" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G45))),"",G45*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G45))),"",G45*'参数与来源'!$N$19)</f>
       </c>
       <c r="I45" s="298">
         <f>IF(G45="","",G45*'参数与来源'!$D$8)</f>
       </c>
       <c r="J45" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I45=""),"",I45*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I45=""),"",I45*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K45" s="298">
         <f>IF(E45="","",(E45-$F$8)/(1-$F$11))</f>
@@ -3216,13 +3222,13 @@
         <f>IF(D46="","",E46/D46)</f>
       </c>
       <c r="H46" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G46))),"",G46*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G46))),"",G46*'参数与来源'!$N$19)</f>
       </c>
       <c r="I46" s="298">
         <f>IF(G46="","",G46*'参数与来源'!$D$8)</f>
       </c>
       <c r="J46" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I46=""),"",I46*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I46=""),"",I46*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K46" s="298">
         <f>IF(E46="","",(E46-$F$8)/(1-$F$11))</f>
@@ -3251,13 +3257,13 @@
         <f>IF(D47="","",E47/D47)</f>
       </c>
       <c r="H47" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G47))),"",G47*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G47))),"",G47*'参数与来源'!$N$19)</f>
       </c>
       <c r="I47" s="298">
         <f>IF(G47="","",G47*'参数与来源'!$D$8)</f>
       </c>
       <c r="J47" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I47=""),"",I47*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I47=""),"",I47*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K47" s="298">
         <f>IF(E47="","",(E47-$F$8)/(1-$F$11))</f>
@@ -3286,13 +3292,13 @@
         <f>IF(D48="","",E48/D48)</f>
       </c>
       <c r="H48" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G48))),"",G48*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G48))),"",G48*'参数与来源'!$N$19)</f>
       </c>
       <c r="I48" s="298">
         <f>IF(G48="","",G48*'参数与来源'!$D$8)</f>
       </c>
       <c r="J48" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I48=""),"",I48*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I48=""),"",I48*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K48" s="298">
         <f>IF(E48="","",(E48-$F$8)/(1-$F$11))</f>
@@ -3321,13 +3327,13 @@
         <f>IF(D49="","",E49/D49)</f>
       </c>
       <c r="H49" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G49))),"",G49*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G49))),"",G49*'参数与来源'!$N$19)</f>
       </c>
       <c r="I49" s="298">
         <f>IF(G49="","",G49*'参数与来源'!$D$8)</f>
       </c>
       <c r="J49" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I49=""),"",I49*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I49=""),"",I49*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K49" s="298">
         <f>IF(E49="","",(E49-$F$8)/(1-$F$11))</f>
@@ -3356,13 +3362,13 @@
         <f>IF(D50="","",E50/D50)</f>
       </c>
       <c r="H50" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G50))),"",G50*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G50))),"",G50*'参数与来源'!$N$19)</f>
       </c>
       <c r="I50" s="298">
         <f>IF(G50="","",G50*'参数与来源'!$D$8)</f>
       </c>
       <c r="J50" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I50=""),"",I50*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I50=""),"",I50*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K50" s="298">
         <f>IF(E50="","",(E50-$F$8)/(1-$F$11))</f>
@@ -3391,13 +3397,13 @@
         <f>IF(D51="","",E51/D51)</f>
       </c>
       <c r="H51" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G51))),"",G51*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G51))),"",G51*'参数与来源'!$N$19)</f>
       </c>
       <c r="I51" s="298">
         <f>IF(G51="","",G51*'参数与来源'!$D$8)</f>
       </c>
       <c r="J51" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I51=""),"",I51*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I51=""),"",I51*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K51" s="298">
         <f>IF(E51="","",(E51-$F$8)/(1-$F$11))</f>
@@ -3426,13 +3432,13 @@
         <f>IF(D52="","",E52/D52)</f>
       </c>
       <c r="H52" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G52))),"",G52*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G52))),"",G52*'参数与来源'!$N$19)</f>
       </c>
       <c r="I52" s="298">
         <f>IF(G52="","",G52*'参数与来源'!$D$8)</f>
       </c>
       <c r="J52" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I52=""),"",I52*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I52=""),"",I52*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K52" s="298">
         <f>IF(E52="","",(E52-$F$8)/(1-$F$11))</f>
@@ -3461,13 +3467,13 @@
         <f>IF(D53="","",E53/D53)</f>
       </c>
       <c r="H53" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G53))),"",G53*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G53))),"",G53*'参数与来源'!$N$19)</f>
       </c>
       <c r="I53" s="298">
         <f>IF(G53="","",G53*'参数与来源'!$D$8)</f>
       </c>
       <c r="J53" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I53=""),"",I53*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I53=""),"",I53*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K53" s="298">
         <f>IF(E53="","",(E53-$F$8)/(1-$F$11))</f>
@@ -3496,13 +3502,13 @@
         <f>IF(D54="","",E54/D54)</f>
       </c>
       <c r="H54" s="344">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G54))),"",G54*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G54))),"",G54*'参数与来源'!$N$19)</f>
       </c>
       <c r="I54" s="348">
         <f>IF(G54="","",G54*'参数与来源'!$D$8)</f>
       </c>
       <c r="J54" s="348">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I54=""),"",I54*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I54=""),"",I54*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K54" s="348">
         <f>IF(E54="","",(E54-$F$8)/(1-$F$11))</f>
@@ -3604,13 +3610,13 @@
         <f>E59/D59</f>
       </c>
       <c r="H59" s="275">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G59))),"",G59*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G59))),"",G59*'参数与来源'!$N$19)</f>
       </c>
       <c r="I59" s="279">
         <f>G59*'参数与来源'!$D$8</f>
       </c>
       <c r="J59" s="279">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I59*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I59*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K59" s="363">
         <f>1-G59/$F$14</f>
@@ -3639,13 +3645,13 @@
         <f>E60/D60</f>
       </c>
       <c r="H60" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G60))),"",G60*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G60))),"",G60*'参数与来源'!$N$19)</f>
       </c>
       <c r="I60" s="298">
         <f>G60*'参数与来源'!$D$8</f>
       </c>
       <c r="J60" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I60*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I60*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K60" s="367">
         <f>1-G60/$F$14</f>
@@ -3674,13 +3680,13 @@
         <f>E61/D61</f>
       </c>
       <c r="H61" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G61))),"",G61*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G61))),"",G61*'参数与来源'!$N$19)</f>
       </c>
       <c r="I61" s="298">
         <f>G61*'参数与来源'!$D$8</f>
       </c>
       <c r="J61" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I61*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I61*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K61" s="367">
         <f>1-G61/$F$14</f>
@@ -3709,13 +3715,13 @@
         <f>E62/D62</f>
       </c>
       <c r="H62" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G62))),"",G62*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G62))),"",G62*'参数与来源'!$N$19)</f>
       </c>
       <c r="I62" s="298">
         <f>G62*'参数与来源'!$D$8</f>
       </c>
       <c r="J62" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I62*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I62*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K62" s="367">
         <f>1-G62/$F$14</f>
@@ -3744,13 +3750,13 @@
         <f>E63/D63</f>
       </c>
       <c r="H63" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G63))),"",G63*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G63))),"",G63*'参数与来源'!$N$19)</f>
       </c>
       <c r="I63" s="298">
         <f>G63*'参数与来源'!$D$8</f>
       </c>
       <c r="J63" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I63*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I63*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K63" s="367">
         <f>1-G63/$F$14</f>
@@ -3779,13 +3785,13 @@
         <f>E64/D64</f>
       </c>
       <c r="H64" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G64))),"",G64*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G64))),"",G64*'参数与来源'!$N$19)</f>
       </c>
       <c r="I64" s="298">
         <f>G64*'参数与来源'!$D$8</f>
       </c>
       <c r="J64" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I64*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I64*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K64" s="367">
         <f>1-G64/$F$14</f>
@@ -3814,13 +3820,13 @@
         <f>E65/D65</f>
       </c>
       <c r="H65" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G65))),"",G65*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G65))),"",G65*'参数与来源'!$N$19)</f>
       </c>
       <c r="I65" s="298">
         <f>G65*'参数与来源'!$D$8</f>
       </c>
       <c r="J65" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I65*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I65*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K65" s="367">
         <f>1-G65/$F$14</f>
@@ -3849,13 +3855,13 @@
         <f>E66/D66</f>
       </c>
       <c r="H66" s="294">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G66))),"",G66*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G66))),"",G66*'参数与来源'!$N$19)</f>
       </c>
       <c r="I66" s="298">
         <f>G66*'参数与来源'!$D$8</f>
       </c>
       <c r="J66" s="298">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I66*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I66*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K66" s="367">
         <f>1-G66/$F$14</f>
@@ -3884,13 +3890,13 @@
         <f>E67/D67</f>
       </c>
       <c r="H67" s="344">
-        <f>IF(OR($L$14="",NOT(ISNUMBER(G67))),"",G67*$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G67))),"",G67*'参数与来源'!$N$19)</f>
       </c>
       <c r="I67" s="348">
         <f>G67*'参数与来源'!$D$8</f>
       </c>
       <c r="J67" s="348">
-        <f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I67*$L$14))*'参数与来源'!$N$8,"")</f>
+        <f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I67*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</f>
       </c>
       <c r="K67" s="371">
         <f>1-G67/$F$14</f>
@@ -4528,7 +4534,7 @@
         <v>USD</v>
       </c>
       <c r="F39" s="94" t="str">
-        <v>手动 USDT 价格再换算 USD</v>
+        <v>有效 USDT 价格再换算 USD</v>
       </c>
     </row>
     <row r="40">
@@ -4736,7 +4742,7 @@
         <f>IF(C7&lt;=80%,('参数与来源'!$D$11+F7)/('参数与来源'!$D$12-C7*'参数与来源'!$D$8),K7/J7)</f>
       </c>
       <c r="O7" s="393">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N7))),"",N7*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N7))),"",N7*'参数与来源'!$N$19)</f>
       </c>
       <c r="P7" s="398">
         <f>N7*'参数与来源'!$D$8</f>
@@ -4783,7 +4789,7 @@
         <f>IF(C8&lt;=80%,('参数与来源'!$D$11+F8)/('参数与来源'!$D$12-C8*'参数与来源'!$D$8),K8/J8)</f>
       </c>
       <c r="O8" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N8))),"",N8*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N8))),"",N8*'参数与来源'!$N$19)</f>
       </c>
       <c r="P8" s="416">
         <f>N8*'参数与来源'!$D$8</f>
@@ -4830,7 +4836,7 @@
         <f>IF(C9&lt;=80%,('参数与来源'!$D$11+F9)/('参数与来源'!$D$12-C9*'参数与来源'!$D$8),K9/J9)</f>
       </c>
       <c r="O9" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N9))),"",N9*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N9))),"",N9*'参数与来源'!$N$19)</f>
       </c>
       <c r="P9" s="416">
         <f>N9*'参数与来源'!$D$8</f>
@@ -4877,7 +4883,7 @@
         <f>IF(C10&lt;=80%,('参数与来源'!$D$11+F10)/('参数与来源'!$D$12-C10*'参数与来源'!$D$8),K10/J10)</f>
       </c>
       <c r="O10" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N10))),"",N10*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N10))),"",N10*'参数与来源'!$N$19)</f>
       </c>
       <c r="P10" s="416">
         <f>N10*'参数与来源'!$D$8</f>
@@ -4924,7 +4930,7 @@
         <f>IF(C11&lt;=80%,('参数与来源'!$D$11+F11)/('参数与来源'!$D$12-C11*'参数与来源'!$D$8),K11/J11)</f>
       </c>
       <c r="O11" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N11))),"",N11*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N11))),"",N11*'参数与来源'!$N$19)</f>
       </c>
       <c r="P11" s="416">
         <f>N11*'参数与来源'!$D$8</f>
@@ -4971,7 +4977,7 @@
         <f>IF(C12&lt;=80%,('参数与来源'!$D$11+F12)/('参数与来源'!$D$12-C12*'参数与来源'!$D$8),K12/J12)</f>
       </c>
       <c r="O12" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N12))),"",N12*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N12))),"",N12*'参数与来源'!$N$19)</f>
       </c>
       <c r="P12" s="416">
         <f>N12*'参数与来源'!$D$8</f>
@@ -5018,7 +5024,7 @@
         <f>IF(C13&lt;=80%,('参数与来源'!$D$11+F13)/('参数与来源'!$D$12-C13*'参数与来源'!$D$8),K13/J13)</f>
       </c>
       <c r="O13" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N13))),"",N13*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N13))),"",N13*'参数与来源'!$N$19)</f>
       </c>
       <c r="P13" s="416">
         <f>N13*'参数与来源'!$D$8</f>
@@ -5065,7 +5071,7 @@
         <f>IF(C14&lt;=80%,('参数与来源'!$D$11+F14)/('参数与来源'!$D$12-C14*'参数与来源'!$D$8),K14/J14)</f>
       </c>
       <c r="O14" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N14))),"",N14*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N14))),"",N14*'参数与来源'!$N$19)</f>
       </c>
       <c r="P14" s="416">
         <f>N14*'参数与来源'!$D$8</f>
@@ -5112,7 +5118,7 @@
         <f>IF(C15&lt;=80%,('参数与来源'!$D$11+F15)/('参数与来源'!$D$12-C15*'参数与来源'!$D$8),K15/J15)</f>
       </c>
       <c r="O15" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N15))),"",N15*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N15))),"",N15*'参数与来源'!$N$19)</f>
       </c>
       <c r="P15" s="416">
         <f>N15*'参数与来源'!$D$8</f>
@@ -5159,7 +5165,7 @@
         <f>IF(C16&lt;=80%,('参数与来源'!$D$11+F16)/('参数与来源'!$D$12-C16*'参数与来源'!$D$8),K16/J16)</f>
       </c>
       <c r="O16" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N16))),"",N16*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N16))),"",N16*'参数与来源'!$N$19)</f>
       </c>
       <c r="P16" s="416">
         <f>N16*'参数与来源'!$D$8</f>
@@ -5206,7 +5212,7 @@
         <f>IF(C17&lt;=80%,('参数与来源'!$D$11+F17)/('参数与来源'!$D$12-C17*'参数与来源'!$D$8),K17/J17)</f>
       </c>
       <c r="O17" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N17))),"",N17*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N17))),"",N17*'参数与来源'!$N$19)</f>
       </c>
       <c r="P17" s="416">
         <f>N17*'参数与来源'!$D$8</f>
@@ -5253,7 +5259,7 @@
         <f>IF(C18&lt;=80%,('参数与来源'!$D$11+F18)/('参数与来源'!$D$12-C18*'参数与来源'!$D$8),K18/J18)</f>
       </c>
       <c r="O18" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N18))),"",N18*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N18))),"",N18*'参数与来源'!$N$19)</f>
       </c>
       <c r="P18" s="416">
         <f>N18*'参数与来源'!$D$8</f>
@@ -5300,7 +5306,7 @@
         <f>IF(C19&lt;=80%,('参数与来源'!$D$11+F19)/('参数与来源'!$D$12-C19*'参数与来源'!$D$8),K19/J19)</f>
       </c>
       <c r="O19" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N19))),"",N19*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N19))),"",N19*'参数与来源'!$N$19)</f>
       </c>
       <c r="P19" s="416">
         <f>N19*'参数与来源'!$D$8</f>
@@ -5347,7 +5353,7 @@
         <f>IF(C20&lt;=80%,('参数与来源'!$D$11+F20)/('参数与来源'!$D$12-C20*'参数与来源'!$D$8),K20/J20)</f>
       </c>
       <c r="O20" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N20))),"",N20*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N20))),"",N20*'参数与来源'!$N$19)</f>
       </c>
       <c r="P20" s="416">
         <f>N20*'参数与来源'!$D$8</f>
@@ -5394,7 +5400,7 @@
         <f>IF(C21&lt;=80%,('参数与来源'!$D$11+F21)/('参数与来源'!$D$12-C21*'参数与来源'!$D$8),K21/J21)</f>
       </c>
       <c r="O21" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N21))),"",N21*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N21))),"",N21*'参数与来源'!$N$19)</f>
       </c>
       <c r="P21" s="416">
         <f>N21*'参数与来源'!$D$8</f>
@@ -5441,7 +5447,7 @@
         <f>IF(C22&lt;=80%,('参数与来源'!$D$11+F22)/('参数与来源'!$D$12-C22*'参数与来源'!$D$8),K22/J22)</f>
       </c>
       <c r="O22" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N22))),"",N22*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N22))),"",N22*'参数与来源'!$N$19)</f>
       </c>
       <c r="P22" s="416">
         <f>N22*'参数与来源'!$D$8</f>
@@ -5488,7 +5494,7 @@
         <f>IF(C23&lt;=80%,('参数与来源'!$D$11+F23)/('参数与来源'!$D$12-C23*'参数与来源'!$D$8),K23/J23)</f>
       </c>
       <c r="O23" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N23))),"",N23*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N23))),"",N23*'参数与来源'!$N$19)</f>
       </c>
       <c r="P23" s="416">
         <f>N23*'参数与来源'!$D$8</f>
@@ -5535,7 +5541,7 @@
         <f>IF(C24&lt;=80%,('参数与来源'!$D$11+F24)/('参数与来源'!$D$12-C24*'参数与来源'!$D$8),K24/J24)</f>
       </c>
       <c r="O24" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N24))),"",N24*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N24))),"",N24*'参数与来源'!$N$19)</f>
       </c>
       <c r="P24" s="416">
         <f>N24*'参数与来源'!$D$8</f>
@@ -5582,7 +5588,7 @@
         <f>IF(C25&lt;=80%,('参数与来源'!$D$11+F25)/('参数与来源'!$D$12-C25*'参数与来源'!$D$8),K25/J25)</f>
       </c>
       <c r="O25" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N25))),"",N25*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N25))),"",N25*'参数与来源'!$N$19)</f>
       </c>
       <c r="P25" s="416">
         <f>N25*'参数与来源'!$D$8</f>
@@ -5629,7 +5635,7 @@
         <f>IF(C26&lt;=80%,('参数与来源'!$D$11+F26)/('参数与来源'!$D$12-C26*'参数与来源'!$D$8),K26/J26)</f>
       </c>
       <c r="O26" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N26))),"",N26*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N26))),"",N26*'参数与来源'!$N$19)</f>
       </c>
       <c r="P26" s="416">
         <f>N26*'参数与来源'!$D$8</f>
@@ -5676,7 +5682,7 @@
         <f>IF(C27&lt;=80%,('参数与来源'!$D$11+F27)/('参数与来源'!$D$12-C27*'参数与来源'!$D$8),K27/J27)</f>
       </c>
       <c r="O27" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N27))),"",N27*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N27))),"",N27*'参数与来源'!$N$19)</f>
       </c>
       <c r="P27" s="416">
         <f>N27*'参数与来源'!$D$8</f>
@@ -5723,7 +5729,7 @@
         <f>IF(C28&lt;=80%,('参数与来源'!$D$11+F28)/('参数与来源'!$D$12-C28*'参数与来源'!$D$8),K28/J28)</f>
       </c>
       <c r="O28" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N28))),"",N28*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N28))),"",N28*'参数与来源'!$N$19)</f>
       </c>
       <c r="P28" s="416">
         <f>N28*'参数与来源'!$D$8</f>
@@ -5770,7 +5776,7 @@
         <f>IF(C29&lt;=80%,('参数与来源'!$D$11+F29)/('参数与来源'!$D$12-C29*'参数与来源'!$D$8),K29/J29)</f>
       </c>
       <c r="O29" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N29))),"",N29*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N29))),"",N29*'参数与来源'!$N$19)</f>
       </c>
       <c r="P29" s="416">
         <f>N29*'参数与来源'!$D$8</f>
@@ -5817,7 +5823,7 @@
         <f>IF(C30&lt;=80%,('参数与来源'!$D$11+F30)/('参数与来源'!$D$12-C30*'参数与来源'!$D$8),K30/J30)</f>
       </c>
       <c r="O30" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N30))),"",N30*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N30))),"",N30*'参数与来源'!$N$19)</f>
       </c>
       <c r="P30" s="416">
         <f>N30*'参数与来源'!$D$8</f>
@@ -5864,7 +5870,7 @@
         <f>IF(C31&lt;=80%,('参数与来源'!$D$11+F31)/('参数与来源'!$D$12-C31*'参数与来源'!$D$8),K31/J31)</f>
       </c>
       <c r="O31" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N31))),"",N31*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N31))),"",N31*'参数与来源'!$N$19)</f>
       </c>
       <c r="P31" s="416">
         <f>N31*'参数与来源'!$D$8</f>
@@ -5911,7 +5917,7 @@
         <f>IF(C32&lt;=80%,('参数与来源'!$D$11+F32)/('参数与来源'!$D$12-C32*'参数与来源'!$D$8),K32/J32)</f>
       </c>
       <c r="O32" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N32))),"",N32*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N32))),"",N32*'参数与来源'!$N$19)</f>
       </c>
       <c r="P32" s="416">
         <f>N32*'参数与来源'!$D$8</f>
@@ -5958,7 +5964,7 @@
         <f>IF(C33&lt;=80%,('参数与来源'!$D$11+F33)/('参数与来源'!$D$12-C33*'参数与来源'!$D$8),K33/J33)</f>
       </c>
       <c r="O33" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N33))),"",N33*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N33))),"",N33*'参数与来源'!$N$19)</f>
       </c>
       <c r="P33" s="416">
         <f>N33*'参数与来源'!$D$8</f>
@@ -6005,7 +6011,7 @@
         <f>IF(C34&lt;=80%,('参数与来源'!$D$11+F34)/('参数与来源'!$D$12-C34*'参数与来源'!$D$8),K34/J34)</f>
       </c>
       <c r="O34" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N34))),"",N34*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N34))),"",N34*'参数与来源'!$N$19)</f>
       </c>
       <c r="P34" s="416">
         <f>N34*'参数与来源'!$D$8</f>
@@ -6052,7 +6058,7 @@
         <f>IF(C35&lt;=80%,('参数与来源'!$D$11+F35)/('参数与来源'!$D$12-C35*'参数与来源'!$D$8),K35/J35)</f>
       </c>
       <c r="O35" s="411">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N35))),"",N35*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N35))),"",N35*'参数与来源'!$N$19)</f>
       </c>
       <c r="P35" s="416">
         <f>N35*'参数与来源'!$D$8</f>
@@ -6099,7 +6105,7 @@
         <f>IF(C36&lt;=80%,('参数与来源'!$D$11+F36)/('参数与来源'!$D$12-C36*'参数与来源'!$D$8),K36/J36)</f>
       </c>
       <c r="O36" s="424">
-        <f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N36))),"",N36*'控筹模型'!$L$14)</f>
+        <f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N36))),"",N36*'参数与来源'!$N$19)</f>
       </c>
       <c r="P36" s="429">
         <f>N36*'参数与来源'!$D$8</f>
@@ -6449,7 +6455,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="N8" s="431">
-        <v>0.999177</v>
+        <v>0.999197</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
@@ -6482,7 +6488,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:29.228Z</t>
+          <t>2026-09-18T09:31:01.466Z</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6587,7 @@
         <v>BNB / USDT</v>
       </c>
       <c r="N12">
-        <v>754.1006248142221</v>
+        <v>752.7144296870387</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
@@ -6614,7 +6620,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:29.228Z</t>
+          <t>2026-09-18T09:31:01.466Z</t>
         </is>
       </c>
     </row>
@@ -6677,6 +6683,12 @@
       <c r="K15" s="69" t="str">
         <v>本表不抵扣可能收到的分红，按保守资金流处理</v>
       </c>
+      <c r="M15" t="str">
+        <v>BNC4 / USDT 每日价格</v>
+      </c>
+      <c r="N15" s="434">
+        <v>5.7682</v>
+      </c>
     </row>
     <row r="16">
       <c r="C16" s="41" t="str">
@@ -6691,6 +6703,14 @@
       <c r="F16" s="44" t="str">
         <v>毕业价格 0.0000098 反推</v>
       </c>
+      <c r="M16" t="str">
+        <v>BNC4 价格时间 / UTC</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:31:01.466Z</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="C17" s="41" t="str">
@@ -6705,6 +6725,14 @@
       <c r="F17" s="44" t="str">
         <v>剩余 20%</v>
       </c>
+      <c r="M17" t="str">
+        <v>BNC4 价格来源</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://dexscreener.com/bsc/0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="C18" s="41" t="str">
@@ -6719,6 +6747,14 @@
       <c r="F18" s="44" t="str">
         <v>2,000 × (1 - 2%)</v>
       </c>
+      <c r="M18" t="str">
+        <v>BNC4 指定交易池</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="C19" s="41" t="str">
@@ -6732,6 +6768,12 @@
       </c>
       <c r="F19" s="44" t="str">
         <v>初始 TOKEN × 初始 Quote</v>
+      </c>
+      <c r="M19" t="str">
+        <v>BNC4 有效价格 / USDT</v>
+      </c>
+      <c r="N19" s="434">
+        <f>IF(AND(ISNUMBER('控筹模型'!$L$14),'控筹模型'!$L$14&gt;0),'控筹模型'!$L$14,IF(AND(ISNUMBER($N$15),$N$15&gt;0),$N$15,""))</f>
       </c>
     </row>
     <row r="20">

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -6455,7 +6455,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="N8" s="431">
-        <v>0.999197</v>
+        <v>0.999193</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
         <v>BNB / USDT</v>
       </c>
       <c r="N12">
-        <v>752.7144296870387</v>
+        <v>751.8667564724733</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
         <v>BNC4 / USDT 每日价格</v>
       </c>
       <c r="N15" s="434">
-        <v>5.7682</v>
+        <v>5.7873</v>
       </c>
     </row>
     <row r="16">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
     </row>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -6455,7 +6455,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="N8" s="431">
-        <v>0.999193</v>
+        <v>0.99917</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
         <v>BNB / USDT</v>
       </c>
       <c r="N12">
-        <v>751.8667564724733</v>
+        <v>751.723930862616</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
         <v>BNC4 / USDT 每日价格</v>
       </c>
       <c r="N15" s="434">
-        <v>5.7873</v>
+        <v>5.8494</v>
       </c>
     </row>
     <row r="16">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
     </row>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Rffe7e1a924f44acc"/>
-    <sheet name="控筹测算" sheetId="2" r:id="Rd15db576cb5b4c33"/>
-    <sheet name="内外盘曲线" sheetId="3" r:id="R5319507f9c6c4c5e"/>
-    <sheet name="洗筹明细" sheetId="4" r:id="R0e2c89e81b7e455c"/>
-    <sheet name="参数与来源" sheetId="5" r:id="R65d0f1aaffda4dd3"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R328ec81a6e794482"/>
+    <sheet name="控筹测算" sheetId="2" r:id="Rf163ef75fd0e425f"/>
+    <sheet name="内外盘曲线" sheetId="3" r:id="Re18391e927804b34"/>
+    <sheet name="洗筹明细" sheetId="4" r:id="R7f65398af3cc4597"/>
+    <sheet name="参数与来源" sheetId="5" r:id="R2e9a4f2059594bd8"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -4225,7 +4225,7 @@
         <v>BNC4 / USDT 价格</v>
       </c>
       <c r="D19" s="84">
-        <f>IF('控筹模型'!L14="","",'控筹模型'!L14)</f>
+        <f>IF('参数与来源'!$N$19="","",'参数与来源'!$N$19)</f>
       </c>
       <c r="E19" s="81" t="str">
         <v>可选；留空不输出 USD</v>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4444,7 +4444,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99917</v>
+        <v>0.999175</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4485,7 +4485,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4840,13 +4840,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.8494</v>
+        <v>5.9511</v>
       </c>
       <c r="I14" s="17">
-        <v>751.723930862616</v>
+        <v>751.1396902444516</v>
       </c>
       <c r="J14" s="6">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4444,7 +4444,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999175</v>
+        <v>0.999657</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4485,7 +4485,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4840,13 +4840,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.9511</v>
+        <v>6.1077</v>
       </c>
       <c r="I14" s="17">
-        <v>751.1396902444516</v>
+        <v>763.5118845764097</v>
       </c>
       <c r="J14" s="6">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4444,7 +4444,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999657</v>
+        <v>0.999604</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4485,7 +4485,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4840,13 +4840,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.1077</v>
+        <v>6.4377</v>
       </c>
       <c r="I14" s="17">
-        <v>763.5118845764097</v>
+        <v>752.7981080507881</v>
       </c>
       <c r="J14" s="6">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R7b2608e940484796"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Rce8ed05961904f83"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R07817fff46094703"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R16d2ba0d60314fea"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -773,7 +773,7 @@
         <v>买入税率</v>
       </c>
       <c r="J7" s="37">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,25,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,25,FALSE)</f>
       </c>
       <c r="K7" s="32"/>
       <c r="L7" s="32"/>
@@ -797,7 +797,7 @@
         <v>卖出税率</v>
       </c>
       <c r="J8" s="37">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,26,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,26,FALSE)</f>
       </c>
       <c r="K8" s="32"/>
       <c r="L8" s="32"/>
@@ -848,7 +848,7 @@
         <v>单地址 Gas</v>
       </c>
       <c r="G11" s="36">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,33,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,33,FALSE)</f>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
@@ -871,7 +871,7 @@
         <v>洗筹基础费率</v>
       </c>
       <c r="J12" s="37">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,20,FALSE)</f>
       </c>
       <c r="K12" s="32"/>
       <c r="L12" s="32"/>
@@ -948,7 +948,7 @@
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
       </c>
       <c r="E18" s="31">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
       </c>
       <c r="F18" s="3" t="str">
         <v>原生币 Gas 储备</v>
@@ -957,7 +957,7 @@
         <f>D53*MAX(0,G11)</f>
       </c>
       <c r="H18" s="31">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,4,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,4,FALSE)</f>
       </c>
       <c r="I18" s="3" t="str">
         <v>总折算 / USDT</v>
@@ -1030,7 +1030,7 @@
         <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",$G$50/$J$51-$G$49,IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
       </c>
       <c r="E22" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1050,7 +1050,7 @@
         <f>IF($D$51="可达",$J$41*MAX(0,$G$7-1),"")</f>
       </c>
       <c r="E23" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1072,7 +1072,7 @@
         <f>IF($D$51="可达",$J$52*$D$29,"")</f>
       </c>
       <c r="E24" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -1094,7 +1094,7 @@
         <f>IF($D$51="可达",$G$12,"")</f>
       </c>
       <c r="E25" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1113,10 +1113,10 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="44">
-        <f>IF($D$51&lt;&gt;"可达","",IF($G$40="pons",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(1+$G$42)),"")))</f>
+        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
       </c>
       <c r="E26" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="25" t="str">
-        <v>目标持仓全部洗一轮，以卖出所得买回。补回为小单固定价 + 现有外盘曲线差额的保守预留，损耗仍按目标加缓冲 FDV；非逐笔模拟。Pons 按原批准口径持仓不降、补回为 0。</v>
+        <v>外盘手续费只在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，损耗仍按目标加缓冲 FDV；非逐笔模拟。</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -1282,10 +1282,10 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="44">
-        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,23,FALSE))</f>
+        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,23,FALSE))</f>
       </c>
       <c r="H37" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -1326,7 +1326,7 @@
         <v>模型类型</v>
       </c>
       <c r="G40" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,10,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,10,FALSE)</f>
       </c>
       <c r="H40" s="32"/>
       <c r="I40" s="32"/>
@@ -1342,7 +1342,7 @@
         <v>内盘基础费</v>
       </c>
       <c r="G41" s="39">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,19,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,19,FALSE)</f>
       </c>
       <c r="H41" s="32"/>
       <c r="I41" s="32" t="str">
@@ -1362,7 +1362,7 @@
         <v>外盘基础费</v>
       </c>
       <c r="G42" s="39">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,20,FALSE)</f>
       </c>
       <c r="H42" s="32"/>
       <c r="I42" s="32"/>
@@ -1378,14 +1378,14 @@
         <v>毕业控筹率</v>
       </c>
       <c r="G43" s="39">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,15,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,15,FALSE)</f>
       </c>
       <c r="H43" s="32"/>
       <c r="I43" s="32" t="str">
         <v>模型键</v>
       </c>
       <c r="J43" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,2,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,2,FALSE)</f>
       </c>
       <c r="K43" s="32"/>
       <c r="L43" s="32"/>
@@ -1398,14 +1398,14 @@
         <v>内盘初始 TOKEN</v>
       </c>
       <c r="G44" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,12,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,12,FALSE)</f>
       </c>
       <c r="H44" s="32"/>
       <c r="I44" s="32" t="str">
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J44" s="32">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,7,FALSE))</f>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,7,FALSE))</f>
       </c>
       <c r="K44" s="32"/>
       <c r="L44" s="32"/>
@@ -1415,21 +1415,21 @@
         <v>总供应量</v>
       </c>
       <c r="D45" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,11,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,11,FALSE)</f>
       </c>
       <c r="E45" s="32"/>
       <c r="F45" s="32" t="str">
         <v>内盘初始 Quote</v>
       </c>
       <c r="G45" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,13,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,13,FALSE)</f>
       </c>
       <c r="H45" s="32"/>
       <c r="I45" s="32" t="str">
         <v>税率上限</v>
       </c>
       <c r="J45" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,32,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,32,FALSE)</f>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32"/>
@@ -1442,7 +1442,7 @@
         <v>内盘 K</v>
       </c>
       <c r="G46" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,14,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,14,FALSE)</f>
       </c>
       <c r="H46" s="32"/>
       <c r="I46" s="32" t="str">
@@ -1478,7 +1478,7 @@
         <v>外盘初始 TOKEN</v>
       </c>
       <c r="G48" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,16,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,16,FALSE)</f>
       </c>
       <c r="H48" s="32"/>
       <c r="I48" s="32" t="str">
@@ -1498,7 +1498,7 @@
         <v>外盘初始 Quote</v>
       </c>
       <c r="G49" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,17,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,17,FALSE)</f>
       </c>
       <c r="H49" s="32"/>
       <c r="I49" s="32"/>
@@ -1514,7 +1514,7 @@
         <v>外盘 K</v>
       </c>
       <c r="G50" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,18,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,18,FALSE)</f>
       </c>
       <c r="H50" s="32"/>
       <c r="I50" s="32" t="str">
@@ -1538,7 +1538,7 @@
         <v>永久锁仓 TOKEN</v>
       </c>
       <c r="G51" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,22,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,22,FALSE)</f>
       </c>
       <c r="H51" s="32"/>
       <c r="I51" s="32" t="str">
@@ -1562,7 +1562,7 @@
         <v>一套内盘原值</v>
       </c>
       <c r="G52" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,21,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,21,FALSE)</f>
       </c>
       <c r="H52" s="32"/>
       <c r="I52" s="32" t="str">
@@ -1586,7 +1586,7 @@
         <v>内盘募集 Quote</v>
       </c>
       <c r="G53" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,24,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,24,FALSE)</f>
       </c>
       <c r="H53" s="32"/>
       <c r="I53" s="32"/>
@@ -1613,7 +1613,7 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="39">
-        <f>IF($G$40="pons",1,(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))^2)</f>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
       </c>
       <c r="K54" s="32"/>
       <c r="L54" s="32"/>
@@ -1623,21 +1623,21 @@
         <v>有效价格 / USDT</v>
       </c>
       <c r="D55" s="41">
-        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,6,FALSE),""))</f>
+        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,6,FALSE),""))</f>
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="32" t="str">
         <v>价格来源</v>
       </c>
       <c r="G55" s="32">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,9,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,9,FALSE)</f>
       </c>
       <c r="H55" s="32"/>
       <c r="I55" s="32" t="str">
         <v>目标外盘 TOKEN</v>
       </c>
       <c r="J55" s="32">
-        <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8))))</f>
+        <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
       </c>
       <c r="K55" s="32"/>
       <c r="L55" s="32"/>
@@ -1647,7 +1647,7 @@
         <v>价格时间 / UTC</v>
       </c>
       <c r="D56" s="42">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,8,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,8,FALSE)</f>
       </c>
       <c r="E56" s="32"/>
       <c r="F56" s="32" t="str">
@@ -1661,7 +1661,7 @@
         <v>洗后外盘 TOKEN</v>
       </c>
       <c r="J56" s="32">
-        <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27))))</f>
+        <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
       </c>
       <c r="K56" s="32"/>
       <c r="L56" s="32"/>
@@ -4246,6 +4246,9 @@
     <col min="33" max="33" width="44" hidden="0" customWidth="1"/>
     <col min="34" max="34" width="20" hidden="0" customWidth="1"/>
     <col min="35" max="35" width="20" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="20" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="44" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="44" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4284,6 +4287,9 @@
       <c r="AG1" s="5"/>
       <c r="AH1" s="5"/>
       <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="5"/>
@@ -4323,6 +4329,9 @@
       <c r="AG2" s="7"/>
       <c r="AH2" s="7"/>
       <c r="AI2" s="7"/>
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="7"/>
+      <c r="AL2" s="7"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="5"/>
@@ -4362,6 +4371,9 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="5"/>
@@ -4399,6 +4411,9 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="5"/>
@@ -4436,6 +4451,9 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="5"/>
@@ -4477,6 +4495,9 @@
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="5"/>
@@ -4518,6 +4539,9 @@
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="5"/>
@@ -4561,6 +4585,9 @@
       <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
+      <c r="AK8" s="5"/>
+      <c r="AL8" s="5"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="5"/>
@@ -4598,6 +4625,9 @@
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="5"/>
@@ -4639,6 +4669,9 @@
       <c r="AG10" s="5"/>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="5"/>
@@ -4647,7 +4680,7 @@
         <v>洗筹与补回口径</v>
       </c>
       <c r="D11" s="12" t="str">
-        <v>损耗按目标加缓冲的 FDV × 双边费率。非 Pons 的补回按目标持仓洗一轮、小单固定价及现有外盘曲线差额估算；Pons 按原批准的 Quote 预算承担手续费，补回为 0。非逐笔模拟。</v>
+        <v>损耗按目标加缓冲的 FDV × 双边费率。外盘手续费仅在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，非逐笔模拟。</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -4680,6 +4713,9 @@
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
+      <c r="AJ11" s="5"/>
+      <c r="AK11" s="5"/>
+      <c r="AL11" s="5"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="5"/>
@@ -4717,6 +4753,9 @@
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="5"/>
+      <c r="AL12" s="5"/>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="5"/>
@@ -4820,6 +4859,15 @@
       <c r="AI13" s="16" t="str">
         <v>单地址 Gas</v>
       </c>
+      <c r="AJ13" s="16" t="str">
+        <v>外盘扣费资产</v>
+      </c>
+      <c r="AK13" s="16" t="str">
+        <v>外盘扣费机制</v>
+      </c>
+      <c r="AL13" s="16" t="str">
+        <v>扣费机制来源</v>
+      </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="5"/>
@@ -4928,6 +4976,15 @@
       </c>
       <c r="AI14" s="5" t="n">
         <v>0.01</v>
+      </c>
+      <c r="AJ14" s="18" t="str">
+        <v>input</v>
+      </c>
+      <c r="AK14" s="21" t="str">
+        <v>PancakeSwap LP 费从输入币扣取；外盘买税扣输出 TOKEN，卖税扣输入 TOKEN</v>
+      </c>
+      <c r="AL14" s="21" t="str">
+        <v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</v>
       </c>
     </row>
   </sheetData>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R07817fff46094703"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R16d2ba0d60314fea"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R27bba28ac3784fbe"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Rd287077c4913490c"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1027,7 +1027,7 @@
         <f>"预算 "&amp;TEXT($D$52,"0%")&amp;" 理论资金"</f>
       </c>
       <c r="D22" s="44">
-        <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",$G$50/$J$51-$G$49,IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
+        <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",($G$50/$J$51-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
       </c>
       <c r="E22" s="3">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -1545,7 +1545,7 @@
         <v>预算交换 TOKEN</v>
       </c>
       <c r="J51" s="32">
-        <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$48)</f>
+        <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)</f>
       </c>
       <c r="K51" s="32"/>
       <c r="L51" s="32"/>
@@ -1599,7 +1599,7 @@
         <v>当前控筹上限</v>
       </c>
       <c r="D54" s="39">
-        <f>IF($G$40="pons",MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$48)*$G$48/$D$45),IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
+        <f>IF($G$40="pons",1-$G$51/$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
       </c>
       <c r="E54" s="32"/>
       <c r="F54" s="32" t="str">
@@ -2075,7 +2075,7 @@
         <f>IF($G$40="pons",$G$43,80%)</f>
       </c>
       <c r="D72" s="56">
-        <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
       </c>
       <c r="E72" s="56">
         <f>IF(D72="","",IF(ABS(C72-$G$43)&lt;0.000001,$G$49,$G$50/D72))</f>
@@ -2099,7 +2099,7 @@
         <f>IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),0,J72*(1+$G$42))</f>
       </c>
       <c r="L72" s="65">
-        <f>IF(D72="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C72-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
+        <f>IF(D72="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C72-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2107,7 +2107,7 @@
         <f>IF($G$40="pons",80%+0*0.5%,IF(80.5%+0*0.5%&lt;=100%,80.5%+0*0.5%,""))</f>
       </c>
       <c r="D73" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
       </c>
       <c r="E73" s="57">
         <f>IF(D73="","",IF(ABS(C73-$G$43)&lt;0.000001,$G$49,$G$50/D73))</f>
@@ -2131,7 +2131,7 @@
         <f>IF(D73="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L73-L72,J73*(1+$G$42)))</f>
       </c>
       <c r="L73" s="66">
-        <f>IF(D73="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
+        <f>IF(D73="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C73-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2139,7 +2139,7 @@
         <f>IF($G$40="pons",80%+1*0.5%,IF(80.5%+1*0.5%&lt;=100%,80.5%+1*0.5%,""))</f>
       </c>
       <c r="D74" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
       </c>
       <c r="E74" s="57">
         <f>IF(D74="","",IF(ABS(C74-$G$43)&lt;0.000001,$G$49,$G$50/D74))</f>
@@ -2163,7 +2163,7 @@
         <f>IF(D74="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L74-L73,J74*(1+$G$42)))</f>
       </c>
       <c r="L74" s="66">
-        <f>IF(D74="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
+        <f>IF(D74="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C74-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2171,7 +2171,7 @@
         <f>IF($G$40="pons",80%+2*0.5%,IF(80.5%+2*0.5%&lt;=100%,80.5%+2*0.5%,""))</f>
       </c>
       <c r="D75" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
       </c>
       <c r="E75" s="57">
         <f>IF(D75="","",IF(ABS(C75-$G$43)&lt;0.000001,$G$49,$G$50/D75))</f>
@@ -2195,7 +2195,7 @@
         <f>IF(D75="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L75-L74,J75*(1+$G$42)))</f>
       </c>
       <c r="L75" s="66">
-        <f>IF(D75="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
+        <f>IF(D75="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C75-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         <f>IF($G$40="pons",80%+3*0.5%,IF(80.5%+3*0.5%&lt;=100%,80.5%+3*0.5%,""))</f>
       </c>
       <c r="D76" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
       </c>
       <c r="E76" s="57">
         <f>IF(D76="","",IF(ABS(C76-$G$43)&lt;0.000001,$G$49,$G$50/D76))</f>
@@ -2227,7 +2227,7 @@
         <f>IF(D76="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L76-L75,J76*(1+$G$42)))</f>
       </c>
       <c r="L76" s="66">
-        <f>IF(D76="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
+        <f>IF(D76="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C76-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2235,7 +2235,7 @@
         <f>IF($G$40="pons",80%+4*0.5%,IF(80.5%+4*0.5%&lt;=100%,80.5%+4*0.5%,""))</f>
       </c>
       <c r="D77" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
       </c>
       <c r="E77" s="57">
         <f>IF(D77="","",IF(ABS(C77-$G$43)&lt;0.000001,$G$49,$G$50/D77))</f>
@@ -2259,7 +2259,7 @@
         <f>IF(D77="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L77-L76,J77*(1+$G$42)))</f>
       </c>
       <c r="L77" s="66">
-        <f>IF(D77="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
+        <f>IF(D77="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C77-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2267,7 +2267,7 @@
         <f>IF($G$40="pons",80%+5*0.5%,IF(80.5%+5*0.5%&lt;=100%,80.5%+5*0.5%,""))</f>
       </c>
       <c r="D78" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
       </c>
       <c r="E78" s="57">
         <f>IF(D78="","",IF(ABS(C78-$G$43)&lt;0.000001,$G$49,$G$50/D78))</f>
@@ -2291,7 +2291,7 @@
         <f>IF(D78="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L78-L77,J78*(1+$G$42)))</f>
       </c>
       <c r="L78" s="66">
-        <f>IF(D78="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
+        <f>IF(D78="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C78-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -2299,7 +2299,7 @@
         <f>IF($G$40="pons",80%+6*0.5%,IF(80.5%+6*0.5%&lt;=100%,80.5%+6*0.5%,""))</f>
       </c>
       <c r="D79" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
       </c>
       <c r="E79" s="57">
         <f>IF(D79="","",IF(ABS(C79-$G$43)&lt;0.000001,$G$49,$G$50/D79))</f>
@@ -2323,7 +2323,7 @@
         <f>IF(D79="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L79-L78,J79*(1+$G$42)))</f>
       </c>
       <c r="L79" s="66">
-        <f>IF(D79="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
+        <f>IF(D79="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C79-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -2331,7 +2331,7 @@
         <f>IF($G$40="pons",80%+7*0.5%,IF(80.5%+7*0.5%&lt;=100%,80.5%+7*0.5%,""))</f>
       </c>
       <c r="D80" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
       </c>
       <c r="E80" s="57">
         <f>IF(D80="","",IF(ABS(C80-$G$43)&lt;0.000001,$G$49,$G$50/D80))</f>
@@ -2355,7 +2355,7 @@
         <f>IF(D80="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L80-L79,J80*(1+$G$42)))</f>
       </c>
       <c r="L80" s="66">
-        <f>IF(D80="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
+        <f>IF(D80="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C80-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -2363,7 +2363,7 @@
         <f>IF($G$40="pons",80%+8*0.5%,IF(80.5%+8*0.5%&lt;=100%,80.5%+8*0.5%,""))</f>
       </c>
       <c r="D81" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
       </c>
       <c r="E81" s="57">
         <f>IF(D81="","",IF(ABS(C81-$G$43)&lt;0.000001,$G$49,$G$50/D81))</f>
@@ -2387,7 +2387,7 @@
         <f>IF(D81="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L81-L80,J81*(1+$G$42)))</f>
       </c>
       <c r="L81" s="66">
-        <f>IF(D81="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
+        <f>IF(D81="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C81-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -2395,7 +2395,7 @@
         <f>IF($G$40="pons",80%+9*0.5%,IF(80.5%+9*0.5%&lt;=100%,80.5%+9*0.5%,""))</f>
       </c>
       <c r="D82" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
       </c>
       <c r="E82" s="57">
         <f>IF(D82="","",IF(ABS(C82-$G$43)&lt;0.000001,$G$49,$G$50/D82))</f>
@@ -2419,7 +2419,7 @@
         <f>IF(D82="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L82-L81,J82*(1+$G$42)))</f>
       </c>
       <c r="L82" s="66">
-        <f>IF(D82="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
+        <f>IF(D82="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C82-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -2427,7 +2427,7 @@
         <f>IF($G$40="pons",80%+10*0.5%,IF(80.5%+10*0.5%&lt;=100%,80.5%+10*0.5%,""))</f>
       </c>
       <c r="D83" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
       </c>
       <c r="E83" s="57">
         <f>IF(D83="","",IF(ABS(C83-$G$43)&lt;0.000001,$G$49,$G$50/D83))</f>
@@ -2451,7 +2451,7 @@
         <f>IF(D83="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L83-L82,J83*(1+$G$42)))</f>
       </c>
       <c r="L83" s="66">
-        <f>IF(D83="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
+        <f>IF(D83="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C83-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -2459,7 +2459,7 @@
         <f>IF($G$40="pons",80%+11*0.5%,IF(80.5%+11*0.5%&lt;=100%,80.5%+11*0.5%,""))</f>
       </c>
       <c r="D84" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
       </c>
       <c r="E84" s="57">
         <f>IF(D84="","",IF(ABS(C84-$G$43)&lt;0.000001,$G$49,$G$50/D84))</f>
@@ -2483,7 +2483,7 @@
         <f>IF(D84="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L84-L83,J84*(1+$G$42)))</f>
       </c>
       <c r="L84" s="66">
-        <f>IF(D84="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
+        <f>IF(D84="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C84-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -2491,7 +2491,7 @@
         <f>IF($G$40="pons",80%+12*0.5%,IF(80.5%+12*0.5%&lt;=100%,80.5%+12*0.5%,""))</f>
       </c>
       <c r="D85" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
       </c>
       <c r="E85" s="57">
         <f>IF(D85="","",IF(ABS(C85-$G$43)&lt;0.000001,$G$49,$G$50/D85))</f>
@@ -2515,7 +2515,7 @@
         <f>IF(D85="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L85-L84,J85*(1+$G$42)))</f>
       </c>
       <c r="L85" s="66">
-        <f>IF(D85="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
+        <f>IF(D85="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C85-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -2523,7 +2523,7 @@
         <f>IF($G$40="pons",80%+13*0.5%,IF(80.5%+13*0.5%&lt;=100%,80.5%+13*0.5%,""))</f>
       </c>
       <c r="D86" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
       </c>
       <c r="E86" s="57">
         <f>IF(D86="","",IF(ABS(C86-$G$43)&lt;0.000001,$G$49,$G$50/D86))</f>
@@ -2547,7 +2547,7 @@
         <f>IF(D86="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L86-L85,J86*(1+$G$42)))</f>
       </c>
       <c r="L86" s="66">
-        <f>IF(D86="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C86-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
+        <f>IF(D86="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C86-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -2555,7 +2555,7 @@
         <f>IF($G$40="pons",80%+14*0.5%,IF(80.5%+14*0.5%&lt;=100%,80.5%+14*0.5%,""))</f>
       </c>
       <c r="D87" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
       </c>
       <c r="E87" s="57">
         <f>IF(D87="","",IF(ABS(C87-$G$43)&lt;0.000001,$G$49,$G$50/D87))</f>
@@ -2579,7 +2579,7 @@
         <f>IF(D87="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L87-L86,J87*(1+$G$42)))</f>
       </c>
       <c r="L87" s="66">
-        <f>IF(D87="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C87-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
+        <f>IF(D87="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C87-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -2587,7 +2587,7 @@
         <f>IF($G$40="pons",80%+15*0.5%,IF(80.5%+15*0.5%&lt;=100%,80.5%+15*0.5%,""))</f>
       </c>
       <c r="D88" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
       </c>
       <c r="E88" s="57">
         <f>IF(D88="","",IF(ABS(C88-$G$43)&lt;0.000001,$G$49,$G$50/D88))</f>
@@ -2611,7 +2611,7 @@
         <f>IF(D88="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L88-L87,J88*(1+$G$42)))</f>
       </c>
       <c r="L88" s="66">
-        <f>IF(D88="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C88-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
+        <f>IF(D88="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C88-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -2619,7 +2619,7 @@
         <f>IF($G$40="pons",80%+16*0.5%,IF(80.5%+16*0.5%&lt;=100%,80.5%+16*0.5%,""))</f>
       </c>
       <c r="D89" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
       </c>
       <c r="E89" s="57">
         <f>IF(D89="","",IF(ABS(C89-$G$43)&lt;0.000001,$G$49,$G$50/D89))</f>
@@ -2643,7 +2643,7 @@
         <f>IF(D89="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L89-L88,J89*(1+$G$42)))</f>
       </c>
       <c r="L89" s="66">
-        <f>IF(D89="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C89-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
+        <f>IF(D89="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C89-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -2651,7 +2651,7 @@
         <f>IF($G$40="pons",80%+17*0.5%,IF(80.5%+17*0.5%&lt;=100%,80.5%+17*0.5%,""))</f>
       </c>
       <c r="D90" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
       </c>
       <c r="E90" s="57">
         <f>IF(D90="","",IF(ABS(C90-$G$43)&lt;0.000001,$G$49,$G$50/D90))</f>
@@ -2675,7 +2675,7 @@
         <f>IF(D90="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L90-L89,J90*(1+$G$42)))</f>
       </c>
       <c r="L90" s="66">
-        <f>IF(D90="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C90-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
+        <f>IF(D90="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C90-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -2683,7 +2683,7 @@
         <f>IF($G$40="pons",80%+18*0.5%,IF(80.5%+18*0.5%&lt;=100%,80.5%+18*0.5%,""))</f>
       </c>
       <c r="D91" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
       </c>
       <c r="E91" s="57">
         <f>IF(D91="","",IF(ABS(C91-$G$43)&lt;0.000001,$G$49,$G$50/D91))</f>
@@ -2707,7 +2707,7 @@
         <f>IF(D91="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L91-L90,J91*(1+$G$42)))</f>
       </c>
       <c r="L91" s="66">
-        <f>IF(D91="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C91-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
+        <f>IF(D91="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C91-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -2715,7 +2715,7 @@
         <f>IF($G$40="pons",80%+19*0.5%,IF(80.5%+19*0.5%&lt;=100%,80.5%+19*0.5%,""))</f>
       </c>
       <c r="D92" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
       </c>
       <c r="E92" s="57">
         <f>IF(D92="","",IF(ABS(C92-$G$43)&lt;0.000001,$G$49,$G$50/D92))</f>
@@ -2739,7 +2739,7 @@
         <f>IF(D92="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L92-L91,J92*(1+$G$42)))</f>
       </c>
       <c r="L92" s="66">
-        <f>IF(D92="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C92-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
+        <f>IF(D92="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C92-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -2747,7 +2747,7 @@
         <f>IF($G$40="pons",80%+20*0.5%,IF(80.5%+20*0.5%&lt;=100%,80.5%+20*0.5%,""))</f>
       </c>
       <c r="D93" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
       </c>
       <c r="E93" s="57">
         <f>IF(D93="","",IF(ABS(C93-$G$43)&lt;0.000001,$G$49,$G$50/D93))</f>
@@ -2771,7 +2771,7 @@
         <f>IF(D93="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L93-L92,J93*(1+$G$42)))</f>
       </c>
       <c r="L93" s="66">
-        <f>IF(D93="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C93-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
+        <f>IF(D93="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C93-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -2779,7 +2779,7 @@
         <f>IF($G$40="pons",80%+21*0.5%,IF(80.5%+21*0.5%&lt;=100%,80.5%+21*0.5%,""))</f>
       </c>
       <c r="D94" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
       </c>
       <c r="E94" s="57">
         <f>IF(D94="","",IF(ABS(C94-$G$43)&lt;0.000001,$G$49,$G$50/D94))</f>
@@ -2803,7 +2803,7 @@
         <f>IF(D94="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L94-L93,J94*(1+$G$42)))</f>
       </c>
       <c r="L94" s="66">
-        <f>IF(D94="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C94-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
+        <f>IF(D94="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C94-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -2811,7 +2811,7 @@
         <f>IF($G$40="pons",80%+22*0.5%,IF(80.5%+22*0.5%&lt;=100%,80.5%+22*0.5%,""))</f>
       </c>
       <c r="D95" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
       </c>
       <c r="E95" s="57">
         <f>IF(D95="","",IF(ABS(C95-$G$43)&lt;0.000001,$G$49,$G$50/D95))</f>
@@ -2835,7 +2835,7 @@
         <f>IF(D95="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L95-L94,J95*(1+$G$42)))</f>
       </c>
       <c r="L95" s="66">
-        <f>IF(D95="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C95-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
+        <f>IF(D95="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C95-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -2843,7 +2843,7 @@
         <f>IF($G$40="pons",80%+23*0.5%,IF(80.5%+23*0.5%&lt;=100%,80.5%+23*0.5%,""))</f>
       </c>
       <c r="D96" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
       </c>
       <c r="E96" s="57">
         <f>IF(D96="","",IF(ABS(C96-$G$43)&lt;0.000001,$G$49,$G$50/D96))</f>
@@ -2867,7 +2867,7 @@
         <f>IF(D96="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L96-L95,J96*(1+$G$42)))</f>
       </c>
       <c r="L96" s="66">
-        <f>IF(D96="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C96-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
+        <f>IF(D96="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C96-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -2875,7 +2875,7 @@
         <f>IF($G$40="pons",80%+24*0.5%,IF(80.5%+24*0.5%&lt;=100%,80.5%+24*0.5%,""))</f>
       </c>
       <c r="D97" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
       </c>
       <c r="E97" s="57">
         <f>IF(D97="","",IF(ABS(C97-$G$43)&lt;0.000001,$G$49,$G$50/D97))</f>
@@ -2899,7 +2899,7 @@
         <f>IF(D97="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L97-L96,J97*(1+$G$42)))</f>
       </c>
       <c r="L97" s="66">
-        <f>IF(D97="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C97-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
+        <f>IF(D97="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C97-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -2907,7 +2907,7 @@
         <f>IF($G$40="pons",80%+25*0.5%,IF(80.5%+25*0.5%&lt;=100%,80.5%+25*0.5%,""))</f>
       </c>
       <c r="D98" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
       </c>
       <c r="E98" s="57">
         <f>IF(D98="","",IF(ABS(C98-$G$43)&lt;0.000001,$G$49,$G$50/D98))</f>
@@ -2931,7 +2931,7 @@
         <f>IF(D98="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L98-L97,J98*(1+$G$42)))</f>
       </c>
       <c r="L98" s="66">
-        <f>IF(D98="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C98-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
+        <f>IF(D98="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C98-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -2939,7 +2939,7 @@
         <f>IF($G$40="pons",80%+26*0.5%,IF(80.5%+26*0.5%&lt;=100%,80.5%+26*0.5%,""))</f>
       </c>
       <c r="D99" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
       </c>
       <c r="E99" s="57">
         <f>IF(D99="","",IF(ABS(C99-$G$43)&lt;0.000001,$G$49,$G$50/D99))</f>
@@ -2963,7 +2963,7 @@
         <f>IF(D99="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L99-L98,J99*(1+$G$42)))</f>
       </c>
       <c r="L99" s="66">
-        <f>IF(D99="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C99-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
+        <f>IF(D99="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C99-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -2971,7 +2971,7 @@
         <f>IF($G$40="pons",80%+27*0.5%,IF(80.5%+27*0.5%&lt;=100%,80.5%+27*0.5%,""))</f>
       </c>
       <c r="D100" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
       </c>
       <c r="E100" s="57">
         <f>IF(D100="","",IF(ABS(C100-$G$43)&lt;0.000001,$G$49,$G$50/D100))</f>
@@ -2995,7 +2995,7 @@
         <f>IF(D100="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L100-L99,J100*(1+$G$42)))</f>
       </c>
       <c r="L100" s="66">
-        <f>IF(D100="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C100-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
+        <f>IF(D100="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C100-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         <f>IF($G$40="pons",80%+28*0.5%,IF(80.5%+28*0.5%&lt;=100%,80.5%+28*0.5%,""))</f>
       </c>
       <c r="D101" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
       </c>
       <c r="E101" s="57">
         <f>IF(D101="","",IF(ABS(C101-$G$43)&lt;0.000001,$G$49,$G$50/D101))</f>
@@ -3027,7 +3027,7 @@
         <f>IF(D101="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L101-L100,J101*(1+$G$42)))</f>
       </c>
       <c r="L101" s="66">
-        <f>IF(D101="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C101-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
+        <f>IF(D101="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C101-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3035,7 +3035,7 @@
         <f>IF($G$40="pons",80%+29*0.5%,IF(80.5%+29*0.5%&lt;=100%,80.5%+29*0.5%,""))</f>
       </c>
       <c r="D102" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
       </c>
       <c r="E102" s="57">
         <f>IF(D102="","",IF(ABS(C102-$G$43)&lt;0.000001,$G$49,$G$50/D102))</f>
@@ -3059,7 +3059,7 @@
         <f>IF(D102="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L102-L101,J102*(1+$G$42)))</f>
       </c>
       <c r="L102" s="66">
-        <f>IF(D102="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C102-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
+        <f>IF(D102="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C102-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3067,7 +3067,7 @@
         <f>IF($G$40="pons",80%+30*0.5%,IF(80.5%+30*0.5%&lt;=100%,80.5%+30*0.5%,""))</f>
       </c>
       <c r="D103" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
       </c>
       <c r="E103" s="57">
         <f>IF(D103="","",IF(ABS(C103-$G$43)&lt;0.000001,$G$49,$G$50/D103))</f>
@@ -3091,7 +3091,7 @@
         <f>IF(D103="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L103-L102,J103*(1+$G$42)))</f>
       </c>
       <c r="L103" s="66">
-        <f>IF(D103="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C103-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
+        <f>IF(D103="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C103-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3099,7 +3099,7 @@
         <f>IF($G$40="pons",80%+31*0.5%,IF(80.5%+31*0.5%&lt;=100%,80.5%+31*0.5%,""))</f>
       </c>
       <c r="D104" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
       </c>
       <c r="E104" s="57">
         <f>IF(D104="","",IF(ABS(C104-$G$43)&lt;0.000001,$G$49,$G$50/D104))</f>
@@ -3123,7 +3123,7 @@
         <f>IF(D104="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L104-L103,J104*(1+$G$42)))</f>
       </c>
       <c r="L104" s="66">
-        <f>IF(D104="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C104-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
+        <f>IF(D104="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C104-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3131,7 +3131,7 @@
         <f>IF($G$40="pons",80%+32*0.5%,IF(80.5%+32*0.5%&lt;=100%,80.5%+32*0.5%,""))</f>
       </c>
       <c r="D105" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
       </c>
       <c r="E105" s="57">
         <f>IF(D105="","",IF(ABS(C105-$G$43)&lt;0.000001,$G$49,$G$50/D105))</f>
@@ -3155,7 +3155,7 @@
         <f>IF(D105="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L105-L104,J105*(1+$G$42)))</f>
       </c>
       <c r="L105" s="66">
-        <f>IF(D105="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C105-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
+        <f>IF(D105="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C105-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3163,7 +3163,7 @@
         <f>IF($G$40="pons",80%+33*0.5%,IF(80.5%+33*0.5%&lt;=100%,80.5%+33*0.5%,""))</f>
       </c>
       <c r="D106" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
       </c>
       <c r="E106" s="57">
         <f>IF(D106="","",IF(ABS(C106-$G$43)&lt;0.000001,$G$49,$G$50/D106))</f>
@@ -3187,7 +3187,7 @@
         <f>IF(D106="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L106-L105,J106*(1+$G$42)))</f>
       </c>
       <c r="L106" s="66">
-        <f>IF(D106="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C106-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
+        <f>IF(D106="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C106-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3195,7 +3195,7 @@
         <f>IF($G$40="pons",80%+34*0.5%,IF(80.5%+34*0.5%&lt;=100%,80.5%+34*0.5%,""))</f>
       </c>
       <c r="D107" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
       </c>
       <c r="E107" s="57">
         <f>IF(D107="","",IF(ABS(C107-$G$43)&lt;0.000001,$G$49,$G$50/D107))</f>
@@ -3219,7 +3219,7 @@
         <f>IF(D107="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L107-L106,J107*(1+$G$42)))</f>
       </c>
       <c r="L107" s="66">
-        <f>IF(D107="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C107-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
+        <f>IF(D107="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C107-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3227,7 +3227,7 @@
         <f>IF($G$40="pons",80%+35*0.5%,IF(80.5%+35*0.5%&lt;=100%,80.5%+35*0.5%,""))</f>
       </c>
       <c r="D108" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
       </c>
       <c r="E108" s="57">
         <f>IF(D108="","",IF(ABS(C108-$G$43)&lt;0.000001,$G$49,$G$50/D108))</f>
@@ -3251,7 +3251,7 @@
         <f>IF(D108="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L108-L107,J108*(1+$G$42)))</f>
       </c>
       <c r="L108" s="66">
-        <f>IF(D108="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C108-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
+        <f>IF(D108="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C108-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3259,7 +3259,7 @@
         <f>IF($G$40="pons",80%+36*0.5%,IF(80.5%+36*0.5%&lt;=100%,80.5%+36*0.5%,""))</f>
       </c>
       <c r="D109" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
       </c>
       <c r="E109" s="57">
         <f>IF(D109="","",IF(ABS(C109-$G$43)&lt;0.000001,$G$49,$G$50/D109))</f>
@@ -3283,7 +3283,7 @@
         <f>IF(D109="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L109-L108,J109*(1+$G$42)))</f>
       </c>
       <c r="L109" s="66">
-        <f>IF(D109="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C109-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
+        <f>IF(D109="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C109-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3291,7 +3291,7 @@
         <f>IF($G$40="pons",80%+37*0.5%,IF(80.5%+37*0.5%&lt;=100%,80.5%+37*0.5%,""))</f>
       </c>
       <c r="D110" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
       </c>
       <c r="E110" s="57">
         <f>IF(D110="","",IF(ABS(C110-$G$43)&lt;0.000001,$G$49,$G$50/D110))</f>
@@ -3315,7 +3315,7 @@
         <f>IF(D110="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L110-L109,J110*(1+$G$42)))</f>
       </c>
       <c r="L110" s="66">
-        <f>IF(D110="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C110-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
+        <f>IF(D110="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C110-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3323,7 +3323,7 @@
         <f>IF($G$40="pons",80%+38*0.5%,IF(80.5%+38*0.5%&lt;=100%,80.5%+38*0.5%,""))</f>
       </c>
       <c r="D111" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
       </c>
       <c r="E111" s="57">
         <f>IF(D111="","",IF(ABS(C111-$G$43)&lt;0.000001,$G$49,$G$50/D111))</f>
@@ -3347,7 +3347,7 @@
         <f>IF(D111="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L111-L110,J111*(1+$G$42)))</f>
       </c>
       <c r="L111" s="66">
-        <f>IF(D111="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C111-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
+        <f>IF(D111="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C111-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3355,7 +3355,7 @@
         <f>IF($G$40="pons",80%+39*0.5%,IF(80.5%+39*0.5%&lt;=100%,80.5%+39*0.5%,""))</f>
       </c>
       <c r="D112" s="57">
-        <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
       </c>
       <c r="E112" s="57">
         <f>IF(D112="","",IF(ABS(C112-$G$43)&lt;0.000001,$G$49,$G$50/D112))</f>
@@ -3379,7 +3379,7 @@
         <f>IF(D112="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L112-L111,J112*(1+$G$42)))</f>
       </c>
       <c r="L112" s="66">
-        <f>IF(D112="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C112-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E112-$G$49)/(1-$G$42),(E112-$G$49)*(1+$G$42))))</f>
+        <f>IF(D112="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C112-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E112-$G$49)/(1-$G$42),(E112-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3387,7 +3387,7 @@
         <f>IF($G$40="pons",80%+40*0.5%,IF(80.5%+40*0.5%&lt;=100%,80.5%+40*0.5%,""))</f>
       </c>
       <c r="D113" s="58">
-        <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
       </c>
       <c r="E113" s="58">
         <f>IF(D113="","",IF(ABS(C113-$G$43)&lt;0.000001,$G$49,$G$50/D113))</f>
@@ -3411,7 +3411,7 @@
         <f>IF(D113="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L113-L112,J113*(1+$G$42)))</f>
       </c>
       <c r="L113" s="67">
-        <f>IF(D113="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C113-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E113-$G$49)/(1-$G$42),(E113-$G$49)*(1+$G$42))))</f>
+        <f>IF(D113="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C113-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E113-$G$49)/(1-$G$42),(E113-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="114" ht="6" customHeight="1">

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R27bba28ac3784fbe"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Rd287077c4913490c"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R2661c30d3e144173"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R794630d80acc47bc"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1113,7 +1113,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="44">
-        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
+        <f>IF($D$51&lt;&gt;"可达","",0)</f>
       </c>
       <c r="E26" s="3">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="C28" s="3" t="str">
-        <v>补回目标控筹率</v>
+        <v>原目标控筹率</v>
       </c>
       <c r="D28" s="38">
         <f>D8</f>
@@ -1200,7 +1200,7 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" ht="20" customHeight="1" hidden="1">
+    <row r="31" ht="20" hidden="1" customHeight="1">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -1212,7 +1212,7 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" ht="20" customHeight="1" hidden="1">
+    <row r="32" ht="20" hidden="1" customHeight="1">
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
@@ -1224,7 +1224,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" ht="20" customHeight="1" hidden="1">
+    <row r="33" ht="20" hidden="1" customHeight="1">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1236,7 +1236,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" ht="20" customHeight="1" hidden="1">
+    <row r="34" ht="20" hidden="1" customHeight="1">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1248,7 +1248,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" ht="20" customHeight="1" hidden="1">
+    <row r="35" ht="20" hidden="1" customHeight="1">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="25" t="str">
-        <v>外盘手续费只在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，损耗仍按目标加缓冲 FDV；非逐笔模拟。</v>
+        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -1318,7 +1318,7 @@
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="40" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
       <c r="E40" s="32"/>
@@ -1334,7 +1334,7 @@
       <c r="K40" s="32"/>
       <c r="L40" s="32"/>
     </row>
-    <row r="41" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="41" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
       <c r="E41" s="32"/>
@@ -1354,7 +1354,7 @@
       <c r="K41" s="32"/>
       <c r="L41" s="32"/>
     </row>
-    <row r="42" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="42" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C42" s="32"/>
       <c r="D42" s="32"/>
       <c r="E42" s="32"/>
@@ -1370,7 +1370,7 @@
       <c r="K42" s="32"/>
       <c r="L42" s="32"/>
     </row>
-    <row r="43" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="43" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C43" s="32"/>
       <c r="D43" s="32"/>
       <c r="E43" s="32"/>
@@ -1390,7 +1390,7 @@
       <c r="K43" s="32"/>
       <c r="L43" s="32"/>
     </row>
-    <row r="44" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="44" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C44" s="32"/>
       <c r="D44" s="32"/>
       <c r="E44" s="32"/>
@@ -1410,7 +1410,7 @@
       <c r="K44" s="32"/>
       <c r="L44" s="32"/>
     </row>
-    <row r="45" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="45" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C45" s="32" t="str">
         <v>总供应量</v>
       </c>
@@ -1434,7 +1434,7 @@
       <c r="K45" s="32"/>
       <c r="L45" s="32"/>
     </row>
-    <row r="46" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="46" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C46" s="32"/>
       <c r="D46" s="32"/>
       <c r="E46" s="32"/>
@@ -1454,7 +1454,7 @@
       <c r="K46" s="32"/>
       <c r="L46" s="32"/>
     </row>
-    <row r="47" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="47" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C47" s="32"/>
       <c r="D47" s="32"/>
       <c r="E47" s="32"/>
@@ -1470,7 +1470,7 @@
       <c r="K47" s="32"/>
       <c r="L47" s="32"/>
     </row>
-    <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="48" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C48" s="32"/>
       <c r="D48" s="32"/>
       <c r="E48" s="32"/>
@@ -1490,7 +1490,7 @@
       <c r="K48" s="32"/>
       <c r="L48" s="32"/>
     </row>
-    <row r="49" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="49" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C49" s="32"/>
       <c r="D49" s="32"/>
       <c r="E49" s="32"/>
@@ -1506,7 +1506,7 @@
       <c r="K49" s="32"/>
       <c r="L49" s="32"/>
     </row>
-    <row r="50" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="50" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C50" s="32"/>
       <c r="D50" s="32"/>
       <c r="E50" s="32"/>
@@ -1526,7 +1526,7 @@
       <c r="K50" s="32"/>
       <c r="L50" s="32"/>
     </row>
-    <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="51" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C51" s="32" t="str">
         <v>目标是否可达</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="K51" s="32"/>
       <c r="L51" s="32"/>
     </row>
-    <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="52" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C52" s="32" t="str">
         <v>预算控筹率</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="K52" s="32"/>
       <c r="L52" s="32"/>
     </row>
-    <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="53" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C53" s="32" t="str">
         <v>地址总数</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="K53" s="32"/>
       <c r="L53" s="32"/>
     </row>
-    <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="54" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C54" s="32" t="str">
         <v>当前控筹上限</v>
       </c>
@@ -1613,12 +1613,12 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="39">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
+        <f>MAX(0,1-$J$29)*MAX(0,1-$J$30)</f>
       </c>
       <c r="K54" s="32"/>
       <c r="L54" s="32"/>
     </row>
-    <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="55" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C55" s="32" t="str">
         <v>有效价格 / USDT</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="K55" s="32"/>
       <c r="L55" s="32"/>
     </row>
-    <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="56" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C56" s="32" t="str">
         <v>价格时间 / UTC</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>洗筹与补回口径</v>
       </c>
       <c r="D11" s="12" t="str">
-        <v>损耗按目标加缓冲的 FDV × 双边费率。外盘手续费仅在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，非逐笔模拟。</v>
+        <v>外盘一卖一买，卖出所得 Quote 全额用于回买。洗后控筹按双边含税费率同价估算，额外补回预留为 0；洗筹损耗预算另列，不计滑点与冲击。</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R2661c30d3e144173"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R794630d80acc47bc"/>
+    <sheet name="控筹模型" sheetId="1" r:id="Re97bbfe24f004914"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R792cbd5cf8404b1e"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1113,7 +1113,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="44">
-        <f>IF($D$51&lt;&gt;"可达","",0)</f>
+        <f>IF($D$51&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(IF($G$40="pons",1/(1-$G$42-$J$48),IF($G$40="four-stock",1/(1-$G$42),1+$G$42)))),""))</f>
       </c>
       <c r="E26" s="3">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="25" t="str">
-        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -1637,7 +1637,7 @@
         <v>目标外盘 TOKEN</v>
       </c>
       <c r="J55" s="32">
-        <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
+        <f>IF($G$40="pons",$G$48-($D$8-$G$43)*$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8))))</f>
       </c>
       <c r="K55" s="32"/>
       <c r="L55" s="32"/>
@@ -1661,7 +1661,7 @@
         <v>洗后外盘 TOKEN</v>
       </c>
       <c r="J56" s="32">
-        <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
+        <f>IF($G$40="pons",$G$48-($D$27-$G$43)*$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27))))</f>
       </c>
       <c r="K56" s="32"/>
       <c r="L56" s="32"/>
@@ -4680,7 +4680,7 @@
         <v>洗筹与补回口径</v>
       </c>
       <c r="D11" s="12" t="str">
-        <v>外盘一卖一买，卖出所得 Quote 全额用于回买。洗后控筹按双边含税费率同价估算，额外补回预留为 0；洗筹损耗预算另列，不计滑点与冲击。</v>
+        <v>外盘一卖一买用卖出所得 Quote 回买；洗后持币按双边费率估算，再按外盘曲线和买入费预留恢复目标所需 Quote。洗筹损耗另列。</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999604</v>
+        <v>0.999767</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.4377</v>
+        <v>6.1429</v>
       </c>
       <c r="I14" s="17">
-        <v>752.7981080507881</v>
+        <v>786.293206317072</v>
       </c>
       <c r="J14" s="6">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Re97bbfe24f004914"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R792cbd5cf8404b1e"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R7df17c9a95394e12"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Rd163d6e651494776"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="7">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <x:numFmt numFmtId="201" formatCode="0.0000000000"/>
     <x:numFmt numFmtId="202" formatCode="@"/>
@@ -23,6 +23,7 @@
     <x:numFmt numFmtId="204" formatCode="#,##0"/>
     <x:numFmt numFmtId="205" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="206" formatCode="0.0000%"/>
+    <x:numFmt numFmtId="207" formatCode=";;;"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -156,7 +157,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="68">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -351,6 +352,9 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="204" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -945,7 +949,7 @@
         <v>建议 Quote 资金</v>
       </c>
       <c r="D18" s="43">
-        <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
+        <f>IF(AND(LEFT($D$51,2)="可达",ISNUMBER($D$22),ISNUMBER($D$23),ISNUMBER($D$25),ISNUMBER($D$26)),SUM($D$22:$D$23,$D$25:$D$26),"")</f>
       </c>
       <c r="E18" s="31">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -1064,13 +1068,9 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="C24" s="3" t="str">
-        <v>洗筹损耗</v>
-      </c>
-      <c r="D24" s="44">
-        <f>IF($D$51="可达",$J$52*$D$29,"")</f>
-      </c>
+    <row r="24" customHeight="1" hidden="1">
+      <c r="C24" s="3"/>
+      <c r="D24" s="68"/>
       <c r="E24" s="3">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
       </c>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="25" t="str">
-        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；手续费仅降低洗后持币，不另列资金。洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -4680,7 +4680,7 @@
         <v>洗筹与补回口径</v>
       </c>
       <c r="D11" s="12" t="str">
-        <v>外盘一卖一买用卖出所得 Quote 回买；洗后持币按双边费率估算，再按外盘曲线和买入费预留恢复目标所需 Quote。洗筹损耗另列。</v>
+        <v>外盘一卖一买用卖出所得 Quote 回买；双边费用仅降低洗后持币，不另列资金；只按外盘曲线和买入费预留恢复目标所需 Quote。</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999812</v>
+        <v>0.999826</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.3413</v>
+        <v>6.02645</v>
       </c>
       <c r="I14" s="17">
-        <v>791.2687585266029</v>
+        <v>772.7044505744</v>
       </c>
       <c r="J14" s="6">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999826</v>
+        <v>0.999818</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.02645</v>
+        <v>6.09988</v>
       </c>
       <c r="I14" s="17">
-        <v>772.7044505744</v>
+        <v>774.2109063849621</v>
       </c>
       <c r="J14" s="6">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999818</v>
+        <v>0.999822</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.09988</v>
+        <v>6.04304</v>
       </c>
       <c r="I14" s="17">
-        <v>774.2109063849621</v>
+        <v>772.4474956542264</v>
       </c>
       <c r="J14" s="6">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999822</v>
+        <v>0.999745</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.04304</v>
+        <v>6.07452</v>
       </c>
       <c r="I14" s="17">
-        <v>772.4474956542264</v>
+        <v>774.4374815577972</v>
       </c>
       <c r="J14" s="6">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999745</v>
+        <v>0.999689</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.07452</v>
+        <v>5.8251</v>
       </c>
       <c r="I14" s="17">
-        <v>774.4374815577972</v>
+        <v>763.5174539281716</v>
       </c>
       <c r="J14" s="6">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999689</v>
+        <v>0.999661</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.8251</v>
+        <v>5.7477</v>
       </c>
       <c r="I14" s="17">
-        <v>763.5174539281716</v>
+        <v>757.7268694087296</v>
       </c>
       <c r="J14" s="6">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999661</v>
+        <v>0.999656</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.7477</v>
+        <v>5.8621</v>
       </c>
       <c r="I14" s="17">
-        <v>757.7268694087296</v>
+        <v>766.6137151180006</v>
       </c>
       <c r="J14" s="6">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999656</v>
+        <v>0.999697</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.8621</v>
+        <v>5.99</v>
       </c>
       <c r="I14" s="17">
-        <v>766.6137151180006</v>
+        <v>777.3055235736429</v>
       </c>
       <c r="J14" s="6">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999697</v>
+        <v>0.999887</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="E8" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.99</v>
+        <v>5.8804</v>
       </c>
       <c r="I14" s="17">
-        <v>777.3055235736429</v>
+        <v>766.2865903847136</v>
       </c>
       <c r="J14" s="6">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AF14" s="21" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG14" s="21" t="inlineStr">

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999887</v>
+        <v>0.999917</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.8804</v>
+        <v>6.01718</v>
       </c>
       <c r="I14" s="17">
-        <v>766.2865903847136</v>
+        <v>787.8753936576736</v>
       </c>
       <c r="J14" s="6">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999917</v>
+        <v>0.999727</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.01718</v>
+        <v>6.06415</v>
       </c>
       <c r="I14" s="17">
-        <v>787.8753936576736</v>
+        <v>794.5869222297687</v>
       </c>
       <c r="J14" s="6">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999727</v>
+        <v>0.999819</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>6.06415</v>
+        <v>5.9258</v>
       </c>
       <c r="I14" s="17">
-        <v>794.5869222297687</v>
+        <v>779.7911421967376</v>
       </c>
       <c r="J14" s="6">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="E8" s="5"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AF14" s="21" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG14" s="21" t="inlineStr">

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999819</v>
+        <v>0.999865</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.9258</v>
+        <v>5.6725</v>
       </c>
       <c r="I14" s="17">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="J14" s="6">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999865</v>
+        <v>0.999439</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.6725</v>
+        <v>5.4507</v>
       </c>
       <c r="I14" s="17">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="J14" s="6">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999439</v>
+        <v>0.999327</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.4507</v>
+        <v>5.2296</v>
       </c>
       <c r="I14" s="17">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="J14" s="6">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999327</v>
+        <v>0.999255</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.2296</v>
+        <v>5.2439</v>
       </c>
       <c r="I14" s="17">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="J14" s="6">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999255</v>
+        <v>0.999127</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.2439</v>
+        <v>5.2782</v>
       </c>
       <c r="I14" s="17">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="J14" s="6">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999127</v>
+        <v>0.999285</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.2782</v>
+        <v>5.2643</v>
       </c>
       <c r="I14" s="17">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="J14" s="6">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999285</v>
+        <v>0.99922</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.2643</v>
+        <v>5.1453</v>
       </c>
       <c r="I14" s="17">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="J14" s="6">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99922</v>
+        <v>0.999272</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.1453</v>
+        <v>5.078</v>
       </c>
       <c r="I14" s="17">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="J14" s="6">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999272</v>
+        <v>0.999087</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.078</v>
+        <v>4.6151</v>
       </c>
       <c r="I14" s="17">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="J14" s="6">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999087</v>
+        <v>0.99913</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>4.6151</v>
+        <v>4.665</v>
       </c>
       <c r="I14" s="17">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="J14" s="6">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99913</v>
+        <v>0.998953</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>4.665</v>
+        <v>4.4552</v>
       </c>
       <c r="I14" s="17">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="J14" s="6">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998953</v>
+        <v>0.999117</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>4.4552</v>
+        <v>4.4504</v>
       </c>
       <c r="I14" s="17">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="J14" s="6">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999117</v>
+        <v>0.999339</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>4.4504</v>
+        <v>4.4181</v>
       </c>
       <c r="I14" s="17">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="J14" s="6">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999339</v>
+        <v>0.999242</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>4.4181</v>
+        <v>4.6464</v>
       </c>
       <c r="I14" s="17">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="J14" s="6">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999242</v>
+        <v>0.999081</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>4.6464</v>
+        <v>5.3259</v>
       </c>
       <c r="I14" s="17">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="J14" s="6">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999081</v>
+        <v>0.99926</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.3259</v>
+        <v>5.3046</v>
       </c>
       <c r="I14" s="17">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="J14" s="6">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99926</v>
+        <v>0.998826</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.3046</v>
+        <v>5.4312</v>
       </c>
       <c r="I14" s="17">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="J14" s="6">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998826</v>
+        <v>0.999098</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.4312</v>
+        <v>5.3912</v>
       </c>
       <c r="I14" s="17">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="J14" s="6">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999098</v>
+        <v>0.999117</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.3912</v>
+        <v>5.5042</v>
       </c>
       <c r="I14" s="17">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="J14" s="6">
-        <v>46319.254710682864</v>
+        <v>46320.26871552083</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999117</v>
+        <v>0.99935</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.5042</v>
+        <v>5.4817</v>
       </c>
       <c r="I14" s="17">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="J14" s="6">
-        <v>46320.26871552083</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99935</v>
+        <v>0.998675</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.4817</v>
+        <v>5.3185</v>
       </c>
       <c r="I14" s="17">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="J14" s="6">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998675</v>
+        <v>0.998741</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.3185</v>
+        <v>5.6161</v>
       </c>
       <c r="I14" s="17">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="J14" s="6">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998741</v>
+        <v>0.998957</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.6161</v>
+        <v>5.4447</v>
       </c>
       <c r="I14" s="17">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="J14" s="6">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998957</v>
+        <v>0.998762</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.4447</v>
+        <v>5.09561</v>
       </c>
       <c r="I14" s="17">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="J14" s="6">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>

--- a/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/latest/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -4462,7 +4462,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998762</v>
+        <v>0.999185</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4506,7 +4506,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4888,13 +4888,13 @@
         <v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</v>
       </c>
       <c r="H14" s="17">
-        <v>5.09561</v>
+        <v>5.003504</v>
       </c>
       <c r="I14" s="17">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="J14" s="6">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>
